--- a/docs/dominio-metrico/migracion/cuestionarios/la-gran-semiramis.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/la-gran-semiramis.xlsx
@@ -21,25 +21,25 @@
     <t>Migración métrica · La gran Semíramis</t>
   </si>
   <si>
-    <t>Para Blanca Ballester Morell · generado el 2026-09-19</t>
-  </si>
-  <si>
-    <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, con este mismo texto. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
-  </si>
-  <si>
-    <t>En Responder están las preguntas que no hemos podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta. Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato. Las preguntas que se refieren a cada estrofa aparecen de dos maneras: si son pocas estrofas, hay una fila por estrofa; si son muchas, hay una sola fila cuya respuesta vale para todas, y las estrofas que se aparten de ella se anotan en «Excepciones / detalle» indicando los versos y la respuesta, por ejemplo «191–194: Cruzada · abab; 203–206: Cruzada · abab».</t>
-  </si>
-  <si>
-    <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiremos a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
-  </si>
-  <si>
-    <t>En Confirmar aparecen las respuestas que hemos rellenado nosotros a partir del término que elegiste en su día: la asonancia de un romance, el esquema de una octava real «regular», o que un endecasílabo suelto «puro» no lleva pareados. Solo hay que revisarlas. Si alguna no es así, elige «No es así» y escribe al lado lo que corresponde.</t>
+    <t>Para Blanca Ballester Morell · generado el 2026-09-20</t>
+  </si>
+  <si>
+    <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, donde estás ahora. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
+  </si>
+  <si>
+    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta. Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato. Las preguntas que se refieren a cada estrofa aparecen de dos maneras: si son pocas estrofas, hay una fila por estrofa; si son muchas, hay una sola fila cuya respuesta vale para todas, y las estrofas que se aparten de ella se anotan en «Excepciones / detalle» indicando los versos y la respuesta, por ejemplo «191–194: Cruzada · abab; 203–206: Cruzada · abab».</t>
+  </si>
+  <si>
+    <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiré a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
+  </si>
+  <si>
+    <t>En Confirmar aparecen las respuestas que he rellenado yo a partir del término que elegiste en su día: la asonancia de un romance, el esquema de una octava real «regular», o que un endecasílabo suelto «puro» no lleva pareados. Solo hay que revisarlas. Si alguna no es así, elige «No es así» y escribe al lado lo que corresponde.</t>
   </si>
   <si>
     <t>En Desviaciones están los versos hipométricos e hipermétricos, las rimas defectuosas y las lagunas que anotaste, con tus notas, y cómo quedan en el modelo nuevo. Se trasladan tal cual. Si tienes a mano el número de sílabas de algún verso hipométrico o hipermétrico, ponlo en la columna «Sílabas»; si no, se registra simplemente que el verso tiene menos o más sílabas de las que le tocan, sin dar una cifra.</t>
   </si>
   <si>
-    <t>Si algo no está claro o no sabes cómo contestarlo, pregúntaselo a David antes de dejarlo a medias. Una vez hecha la migración podrás ver cada secuencia de tu obra con el editor nuevo en el dashboard y corregir allí lo que haga falta.</t>
+    <t>Si algo no está claro o no sabes cómo contestarlo, pregúntamelo antes de dejarlo a medias. Una vez hecha la migración podrás ver cada secuencia de tu obra con el editor nuevo en el dashboard y comprobar allí que la migración no dejó ningún hueco.</t>
   </si>
   <si>
     <t>Cuando no hay desplegable, los formatos son estos:</t>
@@ -147,7 +147,7 @@
     <t>Octava-lira · Heterométrica consonante</t>
   </si>
   <si>
-    <t>Sus 127 versos no encajan con «Heterométrica consonante», que se compone de unidades completas de 8 versos. Encajaría con 1 verso más (128) o con 7 versos menos (120).</t>
+    <t>Sus 127 versos no encajan en una octava-lira heterométrica consonante, que se compone de unidades completas de 8 versos. Encajaría con 1 verso más (128) o con 7 versos menos (120).</t>
   </si>
   <si>
     <t/>
@@ -165,7 +165,7 @@
     <t>Soneto · Endecasílabo consonante</t>
   </si>
   <si>
-    <t>Sus 15 versos no encajan con «Endecasílabo consonante», que se compone de unidades completas de 14 versos. Encajaría con 13 versos más (28) o con 1 verso menos (14).</t>
+    <t>Sus 15 versos no encajan en un soneto endecasílabo consonante, que se compone de unidades completas de 14 versos. Encajaría con 13 versos más (28) o con 1 verso menos (14).</t>
   </si>
   <si>
     <t>L|af7fd9b4-2357-4092-bc21-e17ae8c614d3</t>
@@ -866,7 +866,7 @@
     <t>Heterométrica consonante</t>
   </si>
   <si>
-    <t>Revisar: Sus 127 versos no encajan con «Heterométrica consonante», que se compone de unidades completas de 8 versos. Encajaría con 1 verso más (128) o con 7 versos menos (120).</t>
+    <t>Revisar: Sus 127 versos no encajan en una octava-lira heterométrica consonante, que se compone de unidades completas de 8 versos. Encajaría con 1 verso más (128) o con 7 versos menos (120).</t>
   </si>
   <si>
     <t>18 derivadas</t>
@@ -899,7 +899,7 @@
     <t>Soneto</t>
   </si>
   <si>
-    <t>Revisar: Sus 15 versos no encajan con «Endecasílabo consonante», que se compone de unidades completas de 14 versos. Encajaría con 13 versos más (28) o con 1 verso menos (14).</t>
+    <t>Revisar: Sus 15 versos no encajan en un soneto endecasílabo consonante, que se compone de unidades completas de 14 versos. Encajaría con 13 versos más (28) o con 1 verso menos (14).</t>
   </si>
   <si>
     <t>Falta: Esquema de rima</t>

--- a/docs/dominio-metrico/migracion/cuestionarios/la-gran-semiramis.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/la-gran-semiramis.xlsx
@@ -33,10 +33,10 @@
     <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiré a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
   </si>
   <si>
-    <t>En Confirmar aparecen las respuestas que he rellenado yo a partir del término que elegiste en su día: la asonancia de un romance, el esquema de una octava real «regular», o que un endecasílabo suelto «puro» no lleva pareados. Solo hay que revisarlas. Si alguna no es así, elige «No es así» y escribe al lado lo que corresponde.</t>
-  </si>
-  <si>
-    <t>En Desviaciones están los versos hipométricos e hipermétricos, las rimas defectuosas y las lagunas que anotaste, con tus notas, y cómo quedan en el modelo nuevo. Se trasladan tal cual. Si tienes a mano el número de sílabas de algún verso hipométrico o hipermétrico, ponlo en la columna «Sílabas»; si no, se registra simplemente que el verso tiene menos o más sílabas de las que le tocan, sin dar una cifra.</t>
+    <t>En Confirmar aparecen las respuestas que he rellenado yo a partir del término que elegiste en su día: la asonancia de un romance, el esquema de una octava real «regular», o que un endecasílabo suelto «puro» no lleva pareados. Ahí van también los tramos que vuelven a ser una sola secuencia. Solo hay que revisarlas. Si alguna no es así, elige «No es así» y escribe al lado lo que corresponde.</t>
+  </si>
+  <si>
+    <t>En Desviaciones están los versos hipométricos e hipermétricos, las rimas defectuosas y las lagunas que anotaste, con tus notas, y cómo quedan en el modelo nuevo. Se trasladan tal cual, así que basta con revisarlas: la columna «¿Correcto?» tiene el mismo desplegable que la pestaña anterior y solo hay que tocarla si algo no queda como digo. La columna «Sílabas del verso» es únicamente para los versos hipométricos e hipermétricos, por si tienes a mano cuántas sílabas mide el verso; si no la rellenas, se registra que tiene menos o más de las que le tocan, sin dar una cifra. En las demás filas esa celda está apagada.</t>
   </si>
   <si>
     <t>Si algo no está claro o no sabes cómo contestarlo, pregúntamelo antes de dejarlo a medias. Una vez hecha la migración podrás ver cada secuencia de tu obra con el editor nuevo en el dashboard y comprobar allí que la migración no dejó ningún hueco.</t>
@@ -711,10 +711,10 @@
     <t>Cómo queda</t>
   </si>
   <si>
-    <t>Sílabas</t>
-  </si>
-  <si>
-    <t>Informativa</t>
+    <t>Sílabas del verso</t>
+  </si>
+  <si>
+    <t>Revisar</t>
   </si>
   <si>
     <t>Endecasílabo suelto · Endecasílabo (1226–1312)</t>
@@ -3765,7 +3765,7 @@
     <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="44" customWidth="1"/>
     <col min="6" max="6" width="40" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="30" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
@@ -3901,6 +3901,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="H2:H4">
+      <formula1>Listas!$D$2:$D$3</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/dominio-metrico/migracion/cuestionarios/la-gran-semiramis.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/la-gran-semiramis.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1086" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="257">
   <si>
     <t>Migración métrica · La gran Semíramis</t>
   </si>
   <si>
-    <t>Para Blanca Ballester Morell · generado el 2026-09-20</t>
+    <t>Para Blanca Ballester Morell · generado el 2026-09-21</t>
   </si>
   <si>
     <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, donde estás ahora. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
@@ -63,9 +63,6 @@
     <t>Hay una laguna que no se contó (indico dónde y cuántos versos faltan)</t>
   </si>
   <si>
-    <t>Con seis versos enlazados · abcabcdd · abcabcdd</t>
-  </si>
-  <si>
     <t>Tipología 1 · ababa</t>
   </si>
   <si>
@@ -75,9 +72,6 @@
     <t>El rango está mal (indico el correcto)</t>
   </si>
   <si>
-    <t>Cruzada con pareados · ababccdd · ababccdd</t>
-  </si>
-  <si>
     <t>Tipología 2 · abbab</t>
   </si>
   <si>
@@ -147,7 +141,7 @@
     <t>Octava-lira · Heterométrica consonante</t>
   </si>
   <si>
-    <t>Sus 127 versos no encajan en una octava-lira heterométrica consonante, que se compone de unidades completas de 8 versos. Encajaría con 1 verso más (128) o con 7 versos menos (120).</t>
+    <t>Sus 127 versos no encajan en una octava-lira heterométrica consonante, que se compone de unidades completas de 8 versos. Encajaría con 1 verso más (128) o con 7 versos menos (120). Las preguntas que dependen de cómo se reparta en estrofas te las haré cuando esto esté claro.</t>
   </si>
   <si>
     <t/>
@@ -165,7 +159,7 @@
     <t>Soneto · Endecasílabo consonante</t>
   </si>
   <si>
-    <t>Sus 15 versos no encajan en un soneto endecasílabo consonante, que se compone de unidades completas de 14 versos. Encajaría con 13 versos más (28) o con 1 verso menos (14).</t>
+    <t>Sus 15 versos no encajan en un soneto endecasílabo consonante, que se compone de unidades completas de 14 versos. Encajaría con 13 versos más (28) o con 1 verso menos (14). Las preguntas que dependen de cómo se reparta en estrofas te las haré cuando esto esté claro.</t>
   </si>
   <si>
     <t>L|af7fd9b4-2357-4092-bc21-e17ae8c614d3</t>
@@ -174,220 +168,121 @@
     <t>Responder</t>
   </si>
   <si>
-    <t>Esquema de rima · 15 estrofas</t>
-  </si>
-  <si>
-    <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones» (versos: respuesta)</t>
-  </si>
-  <si>
-    <t>R|e8af1e55-7dc2-4b1b-92d2-99a9f83bc0df|08db5aaa-4193-4fca-9e97-02134010c9c6</t>
-  </si>
-  <si>
-    <t>Medida de cada verso · estrofa 1 (vv. 564–571)</t>
+    <t>1642–1721</t>
+  </si>
+  <si>
+    <t>Quintilla · Octosílaba consonante</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 1 (vv. 1642–1646)</t>
+  </si>
+  <si>
+    <t>Elige en el desplegable</t>
+  </si>
+  <si>
+    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1642</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 2 (vv. 1647–1651)</t>
+  </si>
+  <si>
+    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1647</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 3 (vv. 1652–1656)</t>
+  </si>
+  <si>
+    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1652</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 4 (vv. 1657–1661)</t>
+  </si>
+  <si>
+    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1657</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 5 (vv. 1662–1666)</t>
+  </si>
+  <si>
+    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1662</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 6 (vv. 1667–1671)</t>
+  </si>
+  <si>
+    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1667</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 7 (vv. 1672–1676)</t>
+  </si>
+  <si>
+    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1672</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 8 (vv. 1677–1681)</t>
+  </si>
+  <si>
+    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1677</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 9 (vv. 1682–1686)</t>
+  </si>
+  <si>
+    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1682</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 10 (vv. 1687–1691)</t>
+  </si>
+  <si>
+    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1687</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 11 (vv. 1692–1696)</t>
+  </si>
+  <si>
+    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1692</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 12 (vv. 1697–1701)</t>
+  </si>
+  <si>
+    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1697</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 13 (vv. 1702–1706)</t>
+  </si>
+  <si>
+    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1702</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 14 (vv. 1707–1711)</t>
+  </si>
+  <si>
+    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1707</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 15 (vv. 1712–1716)</t>
+  </si>
+  <si>
+    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1712</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 16 (vv. 1717–1721)</t>
+  </si>
+  <si>
+    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1717</t>
+  </si>
+  <si>
+    <t>1979–2017</t>
+  </si>
+  <si>
+    <t>Canción petrarquista · Regular de 13 versos</t>
+  </si>
+  <si>
+    <t>Remate o envío · Medida de cada verso</t>
   </si>
   <si>
     <t>Escribe el número de sílabas de cada verso, en orden y separados por espacios («7 11 7 7 11»)</t>
-  </si>
-  <si>
-    <t>U|e8af1e55-7dc2-4b1b-92d2-99a9f83bc0df|940d5240-1878-4da4-bc33-c068238be4ef|564</t>
-  </si>
-  <si>
-    <t>Medida de cada verso · estrofa 2 (vv. 572–579)</t>
-  </si>
-  <si>
-    <t>U|e8af1e55-7dc2-4b1b-92d2-99a9f83bc0df|940d5240-1878-4da4-bc33-c068238be4ef|572</t>
-  </si>
-  <si>
-    <t>Medida de cada verso · estrofa 3 (vv. 580–587)</t>
-  </si>
-  <si>
-    <t>U|e8af1e55-7dc2-4b1b-92d2-99a9f83bc0df|940d5240-1878-4da4-bc33-c068238be4ef|580</t>
-  </si>
-  <si>
-    <t>Medida de cada verso · estrofa 4 (vv. 588–595)</t>
-  </si>
-  <si>
-    <t>U|e8af1e55-7dc2-4b1b-92d2-99a9f83bc0df|940d5240-1878-4da4-bc33-c068238be4ef|588</t>
-  </si>
-  <si>
-    <t>Medida de cada verso · estrofa 5 (vv. 596–603)</t>
-  </si>
-  <si>
-    <t>U|e8af1e55-7dc2-4b1b-92d2-99a9f83bc0df|940d5240-1878-4da4-bc33-c068238be4ef|596</t>
-  </si>
-  <si>
-    <t>Medida de cada verso · estrofa 6 (vv. 604–611)</t>
-  </si>
-  <si>
-    <t>U|e8af1e55-7dc2-4b1b-92d2-99a9f83bc0df|940d5240-1878-4da4-bc33-c068238be4ef|604</t>
-  </si>
-  <si>
-    <t>Medida de cada verso · estrofa 7 (vv. 612–619)</t>
-  </si>
-  <si>
-    <t>U|e8af1e55-7dc2-4b1b-92d2-99a9f83bc0df|940d5240-1878-4da4-bc33-c068238be4ef|612</t>
-  </si>
-  <si>
-    <t>Medida de cada verso · estrofa 8 (vv. 620–627)</t>
-  </si>
-  <si>
-    <t>U|e8af1e55-7dc2-4b1b-92d2-99a9f83bc0df|940d5240-1878-4da4-bc33-c068238be4ef|620</t>
-  </si>
-  <si>
-    <t>Medida de cada verso · estrofa 9 (vv. 628–635)</t>
-  </si>
-  <si>
-    <t>U|e8af1e55-7dc2-4b1b-92d2-99a9f83bc0df|940d5240-1878-4da4-bc33-c068238be4ef|628</t>
-  </si>
-  <si>
-    <t>Medida de cada verso · estrofa 10 (vv. 636–643)</t>
-  </si>
-  <si>
-    <t>U|e8af1e55-7dc2-4b1b-92d2-99a9f83bc0df|940d5240-1878-4da4-bc33-c068238be4ef|636</t>
-  </si>
-  <si>
-    <t>Medida de cada verso · estrofa 11 (vv. 644–651)</t>
-  </si>
-  <si>
-    <t>U|e8af1e55-7dc2-4b1b-92d2-99a9f83bc0df|940d5240-1878-4da4-bc33-c068238be4ef|644</t>
-  </si>
-  <si>
-    <t>Medida de cada verso · estrofa 12 (vv. 652–659)</t>
-  </si>
-  <si>
-    <t>U|e8af1e55-7dc2-4b1b-92d2-99a9f83bc0df|940d5240-1878-4da4-bc33-c068238be4ef|652</t>
-  </si>
-  <si>
-    <t>Medida de cada verso · estrofa 13 (vv. 660–667)</t>
-  </si>
-  <si>
-    <t>U|e8af1e55-7dc2-4b1b-92d2-99a9f83bc0df|940d5240-1878-4da4-bc33-c068238be4ef|660</t>
-  </si>
-  <si>
-    <t>Medida de cada verso · estrofa 14 (vv. 668–675)</t>
-  </si>
-  <si>
-    <t>U|e8af1e55-7dc2-4b1b-92d2-99a9f83bc0df|940d5240-1878-4da4-bc33-c068238be4ef|668</t>
-  </si>
-  <si>
-    <t>Medida de cada verso · estrofa 15 (vv. 676–683)</t>
-  </si>
-  <si>
-    <t>U|e8af1e55-7dc2-4b1b-92d2-99a9f83bc0df|940d5240-1878-4da4-bc33-c068238be4ef|676</t>
-  </si>
-  <si>
-    <t>1642–1721</t>
-  </si>
-  <si>
-    <t>Quintilla · Octosílaba consonante</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 1 (vv. 1642–1646)</t>
-  </si>
-  <si>
-    <t>Elige en el desplegable</t>
-  </si>
-  <si>
-    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1642</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 2 (vv. 1647–1651)</t>
-  </si>
-  <si>
-    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1647</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 3 (vv. 1652–1656)</t>
-  </si>
-  <si>
-    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1652</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 4 (vv. 1657–1661)</t>
-  </si>
-  <si>
-    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1657</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 5 (vv. 1662–1666)</t>
-  </si>
-  <si>
-    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1662</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 6 (vv. 1667–1671)</t>
-  </si>
-  <si>
-    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1667</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 7 (vv. 1672–1676)</t>
-  </si>
-  <si>
-    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1672</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 8 (vv. 1677–1681)</t>
-  </si>
-  <si>
-    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1677</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 9 (vv. 1682–1686)</t>
-  </si>
-  <si>
-    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1682</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 10 (vv. 1687–1691)</t>
-  </si>
-  <si>
-    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1687</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 11 (vv. 1692–1696)</t>
-  </si>
-  <si>
-    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1692</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 12 (vv. 1697–1701)</t>
-  </si>
-  <si>
-    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1697</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 13 (vv. 1702–1706)</t>
-  </si>
-  <si>
-    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1702</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 14 (vv. 1707–1711)</t>
-  </si>
-  <si>
-    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1707</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 15 (vv. 1712–1716)</t>
-  </si>
-  <si>
-    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1712</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 16 (vv. 1717–1721)</t>
-  </si>
-  <si>
-    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1717</t>
-  </si>
-  <si>
-    <t>1979–2017</t>
-  </si>
-  <si>
-    <t>Canción petrarquista · Regular de 13 versos</t>
-  </si>
-  <si>
-    <t>Remate o envío · Medida de cada verso</t>
   </si>
   <si>
     <t>R|cc555f52-a64c-4cb8-aa67-afcc5f6cb51d|428ea9b0-de26-4b97-b7bf-67f67f4492c1</t>
@@ -1423,13 +1318,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="4" width="40" customWidth="1"/>
+    <col min="1" max="3" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -1439,11 +1334,8 @@
       <c r="C1" t="s">
         <v>13</v>
       </c>
-      <c r="D1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1453,58 +1345,52 @@
       <c r="C2" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>18</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>19</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>20</v>
       </c>
-      <c r="D3" t="s">
+      <c r="B4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>22</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
         <v>24</v>
       </c>
-      <c r="C5" t="s">
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C6" t="s">
+    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C7" t="s">
+    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C9" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1515,7 +1401,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="11" customWidth="1"/>
@@ -1531,127 +1417,127 @@
   <sheetData>
     <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>37</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="G2" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J2" s="7" t="s">
         <v>44</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="E3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J3" s="7" t="s">
         <v>48</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>52</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>53</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>54</v>
@@ -1659,543 +1545,543 @@
     </row>
     <row r="5" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>55</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J5" s="7" t="s">
         <v>56</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="D6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" s="7" t="s">
         <v>58</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="D7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J7" s="7" t="s">
         <v>60</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="D8" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J8" s="7" t="s">
         <v>62</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="D9" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J9" s="7" t="s">
         <v>64</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="D10" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J10" s="7" t="s">
         <v>66</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="D11" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J11" s="7" t="s">
         <v>68</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="D12" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J12" s="7" t="s">
         <v>70</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="D13" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J13" s="7" t="s">
         <v>72</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="D14" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J14" s="7" t="s">
         <v>74</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="D15" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J15" s="7" t="s">
         <v>76</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="D16" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J16" s="7" t="s">
         <v>78</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="D17" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J17" s="7" t="s">
         <v>80</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="D18" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J18" s="7" t="s">
         <v>82</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="19" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="D19" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J19" s="7" t="s">
         <v>84</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="E20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F20" s="3" t="s">
+      <c r="G20" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J20" s="7" t="s">
         <v>89</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="D21" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>89</v>
-      </c>
       <c r="G21" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J21" s="7" t="s">
         <v>92</v>
@@ -2203,31 +2089,31 @@
     </row>
     <row r="22" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>93</v>
-      </c>
       <c r="E22" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J22" s="7" t="s">
         <v>94</v>
@@ -2235,559 +2121,47 @@
     </row>
     <row r="23" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="D23" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J23" s="7" t="s">
         <v>95</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J24" s="7" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J26" s="7" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J27" s="7" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J28" s="7" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H29" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I29" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J29" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I30" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J30" s="7" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H31" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I31" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J31" s="7" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J32" s="7" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="G33" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H33" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I33" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J33" s="7" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I34" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J34" s="7" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I35" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J35" s="7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I36" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J36" s="7" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="G37" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H37" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I37" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J37" s="7" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="G38" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I38" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J38" s="7" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="G39" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H39" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I39" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J39" s="7" t="s">
-        <v>130</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
   <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G10:G19">
+      <formula1>Listas!$B$2:$B$9</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G2:G3">
       <formula1>Listas!$A$2:$A$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G20:G35">
-      <formula1>Listas!$C$2:$C$9</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G4">
-      <formula1>Listas!$B$2:$B$3</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G4:G19">
+      <formula1>Listas!$B$2:$B$9</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2813,940 +2187,940 @@
   <sheetData>
     <row r="1" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>38</v>
-      </c>
       <c r="I1" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>136</v>
+        <v>101</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>138</v>
+        <v>103</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>140</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>141</v>
+        <v>106</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>143</v>
+        <v>108</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>144</v>
+        <v>109</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>145</v>
+        <v>110</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>146</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>136</v>
+        <v>101</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>138</v>
+        <v>103</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>148</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>151</v>
+        <v>116</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>152</v>
+        <v>117</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>154</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>155</v>
+        <v>120</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>136</v>
+        <v>101</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>138</v>
+        <v>103</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>156</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>157</v>
+        <v>122</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>136</v>
+        <v>101</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>138</v>
+        <v>103</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>158</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>159</v>
+        <v>124</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>143</v>
+        <v>108</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>145</v>
+        <v>110</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>162</v>
+        <v>127</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>136</v>
+        <v>101</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>138</v>
+        <v>103</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>163</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>164</v>
+        <v>129</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>136</v>
+        <v>101</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>138</v>
+        <v>103</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>165</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>151</v>
+        <v>116</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>167</v>
+        <v>132</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>168</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>136</v>
+        <v>101</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>138</v>
+        <v>103</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>170</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>171</v>
+        <v>136</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>143</v>
+        <v>108</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>172</v>
+        <v>137</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>145</v>
+        <v>110</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>173</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>174</v>
+        <v>139</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>136</v>
+        <v>101</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>138</v>
+        <v>103</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>175</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>176</v>
+        <v>141</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="E15" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I15" s="7" t="s">
         <v>143</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>136</v>
+        <v>101</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>138</v>
+        <v>103</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>180</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>181</v>
+        <v>146</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>143</v>
+        <v>108</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>182</v>
+        <v>147</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>145</v>
+        <v>110</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>183</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>184</v>
+        <v>149</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>185</v>
+        <v>150</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>143</v>
+        <v>108</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>186</v>
+        <v>151</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>187</v>
+        <v>152</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>188</v>
+        <v>153</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>189</v>
+        <v>154</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>136</v>
+        <v>101</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>138</v>
+        <v>103</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>190</v>
+        <v>155</v>
       </c>
     </row>
     <row r="20" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>191</v>
+        <v>156</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>143</v>
+        <v>108</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>192</v>
+        <v>157</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>145</v>
+        <v>110</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>193</v>
+        <v>158</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>194</v>
+        <v>159</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>136</v>
+        <v>101</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>138</v>
+        <v>103</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>195</v>
+        <v>160</v>
       </c>
     </row>
     <row r="22" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>196</v>
+        <v>161</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>151</v>
+        <v>116</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>167</v>
+        <v>132</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>197</v>
+        <v>162</v>
       </c>
     </row>
     <row r="23" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>198</v>
+        <v>163</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>199</v>
+        <v>164</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>200</v>
+        <v>165</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>201</v>
+        <v>166</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>202</v>
+        <v>167</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>203</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>204</v>
+        <v>169</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>205</v>
+        <v>170</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>206</v>
+        <v>171</v>
       </c>
     </row>
     <row r="25" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>207</v>
+        <v>172</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>151</v>
+        <v>116</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>208</v>
+        <v>173</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>209</v>
+        <v>174</v>
       </c>
     </row>
     <row r="26" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>210</v>
+        <v>175</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>204</v>
+        <v>169</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>205</v>
+        <v>170</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>211</v>
+        <v>176</v>
       </c>
     </row>
     <row r="27" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>212</v>
+        <v>177</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>151</v>
+        <v>116</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>213</v>
+        <v>178</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>214</v>
+        <v>179</v>
       </c>
     </row>
     <row r="28" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>215</v>
+        <v>180</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>143</v>
+        <v>108</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>216</v>
+        <v>181</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>145</v>
+        <v>110</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>217</v>
+        <v>182</v>
       </c>
     </row>
     <row r="29" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>218</v>
+        <v>183</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>136</v>
+        <v>101</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>138</v>
+        <v>103</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>219</v>
+        <v>184</v>
       </c>
     </row>
     <row r="30" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>220</v>
+        <v>185</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>136</v>
+        <v>101</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>138</v>
+        <v>103</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>221</v>
+        <v>186</v>
       </c>
     </row>
     <row r="31" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>222</v>
+        <v>187</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>136</v>
+        <v>101</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>138</v>
+        <v>103</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>223</v>
+        <v>188</v>
       </c>
     </row>
     <row r="32" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>224</v>
+        <v>189</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>143</v>
+        <v>108</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>225</v>
+        <v>190</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>145</v>
+        <v>110</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>226</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="F10:F32">
-      <formula1>Listas!$D$2:$D$3</formula1>
+      <formula1>Listas!$C$2:$C$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="F2:F32">
-      <formula1>Listas!$D$2:$D$3</formula1>
+      <formula1>Listas!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3773,137 +3147,137 @@
   <sheetData>
     <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>227</v>
+        <v>192</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>228</v>
+        <v>193</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>229</v>
+        <v>194</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>230</v>
+        <v>195</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>231</v>
+        <v>196</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>232</v>
+        <v>197</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>194</v>
+        <v>159</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>233</v>
+        <v>198</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>234</v>
+        <v>199</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>235</v>
+        <v>200</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>236</v>
+        <v>201</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>237</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>232</v>
+        <v>197</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>121</v>
+        <v>85</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>238</v>
+        <v>203</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>234</v>
+        <v>199</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>239</v>
+        <v>204</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>236</v>
+        <v>201</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>240</v>
+        <v>205</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>232</v>
+        <v>197</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>241</v>
+        <v>206</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>234</v>
+        <v>199</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>242</v>
+        <v>207</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>236</v>
+        <v>201</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>243</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="H2:H4">
-      <formula1>Listas!$D$2:$D$3</formula1>
+      <formula1>Listas!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3931,37 +3305,37 @@
   <sheetData>
     <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>244</v>
+        <v>209</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>245</v>
+        <v>210</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>132</v>
+        <v>97</v>
       </c>
       <c r="E1" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="J1" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>34</v>
-      </c>
       <c r="K1" s="5" t="s">
-        <v>250</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3969,34 +3343,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="C2" s="3">
         <v>38</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>251</v>
+        <v>216</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>252</v>
+        <v>217</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>253</v>
+        <v>218</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>254</v>
+        <v>219</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4004,34 +3378,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>141</v>
+        <v>106</v>
       </c>
       <c r="C3" s="3">
         <v>136</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>145</v>
+        <v>110</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>255</v>
+        <v>220</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>256</v>
+        <v>221</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>257</v>
+        <v>222</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>258</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4039,34 +3413,34 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="C4" s="3">
         <v>51</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>251</v>
+        <v>216</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>252</v>
+        <v>217</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>253</v>
+        <v>218</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>254</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4074,34 +3448,34 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="C5" s="3">
         <v>37</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>259</v>
+        <v>224</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>260</v>
+        <v>225</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>261</v>
+        <v>226</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>258</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4109,34 +3483,34 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>155</v>
+        <v>120</v>
       </c>
       <c r="C6" s="3">
         <v>40</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>251</v>
+        <v>216</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>252</v>
+        <v>217</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>253</v>
+        <v>218</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>254</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4144,34 +3518,34 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>262</v>
+        <v>227</v>
       </c>
       <c r="C7" s="3">
         <v>150</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>263</v>
+        <v>228</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>264</v>
+        <v>229</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>265</v>
+        <v>230</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>266</v>
+        <v>231</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>267</v>
+        <v>232</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>268</v>
+        <v>233</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>258</v>
+        <v>223</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4179,34 +3553,34 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>157</v>
+        <v>122</v>
       </c>
       <c r="C8" s="3">
         <v>51</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>251</v>
+        <v>216</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>252</v>
+        <v>217</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>253</v>
+        <v>218</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>254</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4214,34 +3588,34 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>159</v>
+        <v>124</v>
       </c>
       <c r="C9" s="3">
         <v>56</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>145</v>
+        <v>110</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>255</v>
+        <v>220</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>256</v>
+        <v>221</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>269</v>
+        <v>234</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>258</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4249,34 +3623,34 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>162</v>
+        <v>127</v>
       </c>
       <c r="C10" s="3">
         <v>4</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>251</v>
+        <v>216</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>252</v>
+        <v>217</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>253</v>
+        <v>218</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>254</v>
+        <v>219</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4284,34 +3658,34 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C11" s="3">
         <v>127</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>270</v>
+        <v>235</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>271</v>
+        <v>236</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>272</v>
+        <v>237</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>273</v>
+        <v>238</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>258</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4319,34 +3693,34 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>164</v>
+        <v>129</v>
       </c>
       <c r="C12" s="3">
         <v>52</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>251</v>
+        <v>216</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>252</v>
+        <v>217</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>253</v>
+        <v>218</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>254</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4354,34 +3728,34 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="C13" s="3">
         <v>61</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>259</v>
+        <v>224</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>260</v>
+        <v>225</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>261</v>
+        <v>226</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>258</v>
+        <v>223</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4389,34 +3763,34 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="C14" s="3">
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>251</v>
+        <v>216</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>252</v>
+        <v>217</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>253</v>
+        <v>218</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>254</v>
+        <v>219</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4424,34 +3798,34 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>171</v>
+        <v>136</v>
       </c>
       <c r="C15" s="3">
         <v>144</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>145</v>
+        <v>110</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>255</v>
+        <v>220</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>256</v>
+        <v>221</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>274</v>
+        <v>239</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>258</v>
+        <v>223</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4459,34 +3833,34 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>174</v>
+        <v>139</v>
       </c>
       <c r="C16" s="3">
         <v>35</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>251</v>
+        <v>216</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>252</v>
+        <v>217</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>253</v>
+        <v>218</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>254</v>
+        <v>219</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4494,34 +3868,34 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>176</v>
+        <v>141</v>
       </c>
       <c r="C17" s="3">
         <v>24</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>145</v>
+        <v>110</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>255</v>
+        <v>220</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>256</v>
+        <v>221</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>253</v>
+        <v>218</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>258</v>
+        <v>223</v>
       </c>
     </row>
     <row r="18" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4529,34 +3903,34 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="C18" s="3">
         <v>36</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>251</v>
+        <v>216</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>252</v>
+        <v>217</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>253</v>
+        <v>218</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>254</v>
+        <v>219</v>
       </c>
     </row>
     <row r="19" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4564,34 +3938,34 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>181</v>
+        <v>146</v>
       </c>
       <c r="C19" s="3">
         <v>40</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>145</v>
+        <v>110</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>255</v>
+        <v>220</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>256</v>
+        <v>221</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>275</v>
+        <v>240</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>258</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4599,34 +3973,34 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>184</v>
+        <v>149</v>
       </c>
       <c r="C20" s="3">
         <v>108</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>187</v>
+        <v>152</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>276</v>
+        <v>241</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>277</v>
+        <v>242</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>278</v>
+        <v>243</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>258</v>
+        <v>223</v>
       </c>
     </row>
     <row r="21" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4634,34 +4008,34 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>189</v>
+        <v>154</v>
       </c>
       <c r="C21" s="3">
         <v>10</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>251</v>
+        <v>216</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>252</v>
+        <v>217</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>253</v>
+        <v>218</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>254</v>
+        <v>219</v>
       </c>
     </row>
     <row r="22" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4669,34 +4043,34 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>191</v>
+        <v>156</v>
       </c>
       <c r="C22" s="3">
         <v>16</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>145</v>
+        <v>110</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>255</v>
+        <v>220</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>256</v>
+        <v>221</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>279</v>
+        <v>244</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>258</v>
+        <v>223</v>
       </c>
     </row>
     <row r="23" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4704,34 +4078,34 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>194</v>
+        <v>159</v>
       </c>
       <c r="C23" s="3">
         <v>87</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>251</v>
+        <v>216</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>252</v>
+        <v>217</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>234</v>
+        <v>199</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>253</v>
+        <v>218</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>254</v>
+        <v>219</v>
       </c>
     </row>
     <row r="24" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4739,34 +4113,34 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>196</v>
+        <v>161</v>
       </c>
       <c r="C24" s="3">
         <v>61</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>259</v>
+        <v>224</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>260</v>
+        <v>225</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>261</v>
+        <v>226</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>258</v>
+        <v>223</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4774,34 +4148,34 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>198</v>
+        <v>163</v>
       </c>
       <c r="C25" s="3">
         <v>114</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>202</v>
+        <v>167</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>280</v>
+        <v>245</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>281</v>
+        <v>246</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>282</v>
+        <v>247</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>258</v>
+        <v>223</v>
       </c>
     </row>
     <row r="26" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4809,34 +4183,34 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C26" s="3">
         <v>15</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>205</v>
+        <v>170</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>283</v>
+        <v>248</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>261</v>
+        <v>226</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>284</v>
+        <v>249</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>279</v>
+        <v>244</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>258</v>
+        <v>223</v>
       </c>
     </row>
     <row r="27" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4844,34 +4218,34 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>207</v>
+        <v>172</v>
       </c>
       <c r="C27" s="3">
         <v>52</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>259</v>
+        <v>224</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>260</v>
+        <v>225</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>261</v>
+        <v>226</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>258</v>
+        <v>223</v>
       </c>
     </row>
     <row r="28" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4879,34 +4253,34 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>210</v>
+        <v>175</v>
       </c>
       <c r="C28" s="3">
         <v>14</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>205</v>
+        <v>170</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>283</v>
+        <v>248</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>261</v>
+        <v>226</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>279</v>
+        <v>244</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>258</v>
+        <v>223</v>
       </c>
     </row>
     <row r="29" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4914,34 +4288,34 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>212</v>
+        <v>177</v>
       </c>
       <c r="C29" s="3">
         <v>73</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>259</v>
+        <v>224</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>260</v>
+        <v>225</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>261</v>
+        <v>226</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>258</v>
+        <v>223</v>
       </c>
     </row>
     <row r="30" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4949,34 +4323,34 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="C30" s="3">
         <v>80</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>263</v>
+        <v>228</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>264</v>
+        <v>229</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>265</v>
+        <v>230</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>285</v>
+        <v>250</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>258</v>
+        <v>223</v>
       </c>
     </row>
     <row r="31" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4984,34 +4358,34 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>215</v>
+        <v>180</v>
       </c>
       <c r="C31" s="3">
         <v>200</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>145</v>
+        <v>110</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>255</v>
+        <v>220</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>256</v>
+        <v>221</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>286</v>
+        <v>251</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>258</v>
+        <v>223</v>
       </c>
     </row>
     <row r="32" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5019,34 +4393,34 @@
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>218</v>
+        <v>183</v>
       </c>
       <c r="C32" s="3">
         <v>57</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>251</v>
+        <v>216</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>252</v>
+        <v>217</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>253</v>
+        <v>218</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>254</v>
+        <v>219</v>
       </c>
     </row>
     <row r="33" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5054,34 +4428,34 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>121</v>
+        <v>85</v>
       </c>
       <c r="C33" s="3">
         <v>39</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>287</v>
+        <v>252</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>288</v>
+        <v>253</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>289</v>
+        <v>254</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>234</v>
+        <v>199</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>290</v>
+        <v>255</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>258</v>
+        <v>223</v>
       </c>
     </row>
     <row r="34" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5089,34 +4463,34 @@
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>220</v>
+        <v>185</v>
       </c>
       <c r="C34" s="3">
         <v>4</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>251</v>
+        <v>216</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>252</v>
+        <v>217</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>253</v>
+        <v>218</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>254</v>
+        <v>219</v>
       </c>
     </row>
     <row r="35" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5124,34 +4498,34 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="C35" s="3">
         <v>26</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>287</v>
+        <v>252</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>288</v>
+        <v>253</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>289</v>
+        <v>254</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>234</v>
+        <v>199</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>290</v>
+        <v>255</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>258</v>
+        <v>223</v>
       </c>
     </row>
     <row r="36" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5159,34 +4533,34 @@
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>222</v>
+        <v>187</v>
       </c>
       <c r="C36" s="3">
         <v>180</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>251</v>
+        <v>216</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>252</v>
+        <v>217</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>253</v>
+        <v>218</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>254</v>
+        <v>219</v>
       </c>
     </row>
     <row r="37" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5194,34 +4568,34 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>224</v>
+        <v>189</v>
       </c>
       <c r="C37" s="3">
         <v>128</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>145</v>
+        <v>110</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>255</v>
+        <v>220</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>256</v>
+        <v>221</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>291</v>
+        <v>256</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>258</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>

--- a/docs/dominio-metrico/migracion/cuestionarios/la-gran-semiramis.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/la-gran-semiramis.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="257">
   <si>
     <t>Migración métrica · La gran Semíramis</t>
   </si>
@@ -165,6 +165,18 @@
     <t>L|af7fd9b4-2357-4092-bc21-e17ae8c614d3</t>
   </si>
   <si>
+    <t>2022–2047</t>
+  </si>
+  <si>
+    <t>Canción petrarquista · Regular de 13 versos</t>
+  </si>
+  <si>
+    <t>Sus 26 versos no se reparten en las partes que declara una canción petrarquista regular de 13 versos. Puede que el rango esté mal, que se trate de otra forma o que el catálogo no esté admitiendo algo que existe: dime lo que veas y lo consulto.</t>
+  </si>
+  <si>
+    <t>L|9b8f002e-7c47-4d80-b38b-9c73665a522d</t>
+  </si>
+  <si>
     <t>Responder</t>
   </si>
   <si>
@@ -276,13 +288,10 @@
     <t>1979–2017</t>
   </si>
   <si>
-    <t>Canción petrarquista · Regular de 13 versos</t>
-  </si>
-  <si>
     <t>Remate o envío · Medida de cada verso</t>
   </si>
   <si>
-    <t>Escribe el número de sílabas de cada verso, en orden y separados por espacios («7 11 7 7 11»)</t>
+    <t>Escribe el número de sílabas de cada verso, en orden y separados por espacios («7 11 7 7 11»). Solo si este pasaje lleva remate o envío; si no, déjalo en blanco</t>
   </si>
   <si>
     <t>R|cc555f52-a64c-4cb8-aa67-afcc5f6cb51d|428ea9b0-de26-4b97-b7bf-67f67f4492c1</t>
@@ -291,19 +300,10 @@
     <t>Remate o envío · Esquema de rima observado</t>
   </si>
   <si>
-    <t>Escribe una letra por verso, en mayúscula si es de arte mayor y un guion si el verso queda suelto («aBab-B»)</t>
+    <t>Escribe una letra por verso, en mayúscula si es de arte mayor y un guion si el verso queda suelto («aBab-B»). Solo si este pasaje lleva remate o envío; si no, déjalo en blanco</t>
   </si>
   <si>
     <t>R|cc555f52-a64c-4cb8-aa67-afcc5f6cb51d|76ad9ef5-a1d7-4669-a052-a80cbd0fb57d</t>
-  </si>
-  <si>
-    <t>2022–2047</t>
-  </si>
-  <si>
-    <t>R|9b8f002e-7c47-4d80-b38b-9c73665a522d|428ea9b0-de26-4b97-b7bf-67f67f4492c1</t>
-  </si>
-  <si>
-    <t>R|9b8f002e-7c47-4d80-b38b-9c73665a522d|76ad9ef5-a1d7-4669-a052-a80cbd0fb57d</t>
   </si>
   <si>
     <t>Pregunta</t>
@@ -812,7 +812,7 @@
     <t>Regular de 13 versos</t>
   </si>
   <si>
-    <t>Falta: Remate o envío · Medida de cada verso, Remate o envío · Esquema de rima observado</t>
+    <t>Revisar: no se reparte en las partes de su forma</t>
   </si>
   <si>
     <t>16 derivadas</t>
@@ -1401,7 +1401,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="11" customWidth="1"/>
@@ -1513,54 +1513,54 @@
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J4" s="7" t="s">
         <v>52</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>42</v>
@@ -1572,28 +1572,28 @@
         <v>42</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="G6" s="6" t="s">
         <v>42</v>
       </c>
@@ -1604,27 +1604,27 @@
         <v>42</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>42</v>
@@ -1636,27 +1636,27 @@
         <v>42</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>42</v>
@@ -1668,27 +1668,27 @@
         <v>42</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>42</v>
@@ -1700,27 +1700,27 @@
         <v>42</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>42</v>
@@ -1732,27 +1732,27 @@
         <v>42</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>42</v>
@@ -1764,27 +1764,27 @@
         <v>42</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>42</v>
@@ -1796,27 +1796,27 @@
         <v>42</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>42</v>
@@ -1828,27 +1828,27 @@
         <v>42</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>42</v>
@@ -1860,27 +1860,27 @@
         <v>42</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>42</v>
@@ -1892,27 +1892,27 @@
         <v>42</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>42</v>
@@ -1924,27 +1924,27 @@
         <v>42</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>42</v>
@@ -1956,27 +1956,27 @@
         <v>42</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>42</v>
@@ -1988,27 +1988,27 @@
         <v>42</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>42</v>
@@ -2020,18 +2020,18 @@
         <v>42</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>87</v>
@@ -2040,30 +2040,30 @@
         <v>42</v>
       </c>
       <c r="F20" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J20" s="7" t="s">
         <v>88</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>90</v>
@@ -2089,22 +2089,22 @@
     </row>
     <row r="22" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="E22" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>42</v>
@@ -2116,51 +2116,19 @@
         <v>42</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J23" s="7" t="s">
         <v>95</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G10:G19">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G10:G20">
       <formula1>Listas!$B$2:$B$9</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G2:G3">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G2:G4">
       <formula1>Listas!$A$2:$A$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G4:G19">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G5:G20">
       <formula1>Listas!$B$2:$B$9</formula1>
     </dataValidation>
   </dataValidations>
@@ -3214,7 +3182,7 @@
         <v>197</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>203</v>
@@ -3246,7 +3214,7 @@
         <v>197</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>93</v>
+        <v>49</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>206</v>
@@ -4323,7 +4291,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C30" s="3">
         <v>80</v>
@@ -4428,7 +4396,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C33" s="3">
         <v>39</v>
@@ -4449,7 +4417,7 @@
         <v>199</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>255</v>
+        <v>13</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>118</v>
@@ -4498,7 +4466,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>93</v>
+        <v>49</v>
       </c>
       <c r="C35" s="3">
         <v>26</v>

--- a/docs/dominio-metrico/migracion/cuestionarios/la-gran-semiramis.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/la-gran-semiramis.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="269">
   <si>
     <t>Migración métrica · La gran Semíramis</t>
   </si>
@@ -63,6 +63,9 @@
     <t>Hay una laguna que no se contó (indico dónde y cuántos versos faltan)</t>
   </si>
   <si>
+    <t>Con seis versos enlazados · abcabcdd · abcabcdd</t>
+  </si>
+  <si>
     <t>Tipología 1 · ababa</t>
   </si>
   <si>
@@ -72,6 +75,9 @@
     <t>El rango está mal (indico el correcto)</t>
   </si>
   <si>
+    <t>Cruzada con pareados · ababccdd · ababccdd</t>
+  </si>
+  <si>
     <t>Tipología 2 · abbab</t>
   </si>
   <si>
@@ -141,7 +147,7 @@
     <t>Octava-lira · Heterométrica consonante</t>
   </si>
   <si>
-    <t>Sus 127 versos no encajan en una octava-lira heterométrica consonante, que se compone de unidades completas de 8 versos. Encajaría con 1 verso más (128) o con 7 versos menos (120). Las preguntas que dependen de cómo se reparta en estrofas te las haré cuando esto esté claro.</t>
+    <t>Sus 127 versos no encajan en una octava-lira heterométrica consonante, que se compone de unidades completas de 8 versos. Encajaría con 1 verso más (128) o con 7 versos menos (120). Lo demás que te pregunto de este pasaje va contestado de una vez para todas sus estrofas, así que la respuesta vale igual si el rango cambia.</t>
   </si>
   <si>
     <t/>
@@ -159,7 +165,7 @@
     <t>Soneto · Endecasílabo consonante</t>
   </si>
   <si>
-    <t>Sus 15 versos no encajan en un soneto endecasílabo consonante, que se compone de unidades completas de 14 versos. Encajaría con 13 versos más (28) o con 1 verso menos (14). Las preguntas que dependen de cómo se reparta en estrofas te las haré cuando esto esté claro.</t>
+    <t>Sus 15 versos no encajan en un soneto endecasílabo consonante, que se compone de unidades completas de 14 versos. Encajaría con 13 versos más (28) o con 1 verso menos (14).</t>
   </si>
   <si>
     <t>L|af7fd9b4-2357-4092-bc21-e17ae8c614d3</t>
@@ -180,6 +186,24 @@
     <t>Responder</t>
   </si>
   <si>
+    <t>Esquema de rima · todas las estrofas</t>
+  </si>
+  <si>
+    <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones» (versos: respuesta). Cuántas estrofas son depende de lo que decidas arriba, así que contéstalo para todas</t>
+  </si>
+  <si>
+    <t>R|e8af1e55-7dc2-4b1b-92d2-99a9f83bc0df|08db5aaa-4193-4fca-9e97-02134010c9c6</t>
+  </si>
+  <si>
+    <t>Medida de cada verso · todas las estrofas</t>
+  </si>
+  <si>
+    <t>Escribe el número de sílabas de cada verso, en orden y separados por espacios («7 11 7 7 11»). La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones» (versos: respuesta). Cuántas estrofas son depende de lo que decidas arriba, así que contéstalo para todas</t>
+  </si>
+  <si>
+    <t>R|e8af1e55-7dc2-4b1b-92d2-99a9f83bc0df|940d5240-1878-4da4-bc33-c068238be4ef</t>
+  </si>
+  <si>
     <t>1642–1721</t>
   </si>
   <si>
@@ -304,6 +328,18 @@
   </si>
   <si>
     <t>R|cc555f52-a64c-4cb8-aa67-afcc5f6cb51d|76ad9ef5-a1d7-4669-a052-a80cbd0fb57d</t>
+  </si>
+  <si>
+    <t>Escribe el número de sílabas de cada verso, en orden y separados por espacios («7 11 7 7 11»). Solo si este pasaje lleva remate o envío; si no, déjalo en blanco. Cuántas estrofas son depende de lo que decidas arriba, así que contéstalo para todas</t>
+  </si>
+  <si>
+    <t>R|9b8f002e-7c47-4d80-b38b-9c73665a522d|428ea9b0-de26-4b97-b7bf-67f67f4492c1</t>
+  </si>
+  <si>
+    <t>Escribe una letra por verso, en mayúscula si es de arte mayor y un guion si el verso queda suelto («aBab-B»). Solo si este pasaje lleva remate o envío; si no, déjalo en blanco. Cuántas estrofas son depende de lo que decidas arriba, así que contéstalo para todas</t>
+  </si>
+  <si>
+    <t>R|9b8f002e-7c47-4d80-b38b-9c73665a522d|76ad9ef5-a1d7-4669-a052-a80cbd0fb57d</t>
   </si>
   <si>
     <t>Pregunta</t>
@@ -1318,13 +1354,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="3" width="40" customWidth="1"/>
+    <col min="1" max="4" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -1334,8 +1370,11 @@
       <c r="C1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1345,52 +1384,58 @@
       <c r="C2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
+      <c r="C5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
+    <row r="6" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
+    <row r="7" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1401,7 +1446,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="11" customWidth="1"/>
@@ -1417,159 +1462,159 @@
   <sheetData>
     <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="G3" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>57</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J5" s="7" t="s">
         <v>58</v>
@@ -1577,559 +1622,690 @@
     </row>
     <row r="6" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D9" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>57</v>
-      </c>
       <c r="G9" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G10:G20">
-      <formula1>Listas!$B$2:$B$9</formula1>
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G10:G22">
+      <formula1>Listas!$C$2:$C$9</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G2:G4">
       <formula1>Listas!$A$2:$A$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G5:G20">
-      <formula1>Listas!$B$2:$B$9</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G5">
+      <formula1>Listas!$B$2:$B$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G7:G22">
+      <formula1>Listas!$C$2:$C$9</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2155,940 +2331,940 @@
   <sheetData>
     <row r="1" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="20" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
     </row>
     <row r="22" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="23" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
     </row>
     <row r="24" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
     </row>
     <row r="25" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
     </row>
     <row r="26" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
     </row>
     <row r="27" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
     </row>
     <row r="28" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
     </row>
     <row r="29" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="30" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
     </row>
     <row r="31" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
     </row>
     <row r="32" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="F10:F32">
-      <formula1>Listas!$C$2:$C$3</formula1>
+      <formula1>Listas!$D$2:$D$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="F2:F32">
-      <formula1>Listas!$C$2:$C$3</formula1>
+      <formula1>Listas!$D$2:$D$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3115,137 +3291,137 @@
   <sheetData>
     <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="H2:H4">
-      <formula1>Listas!$C$2:$C$3</formula1>
+      <formula1>Listas!$D$2:$D$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3273,37 +3449,37 @@
   <sheetData>
     <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3311,34 +3487,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="C2" s="3">
         <v>38</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3346,34 +3522,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="C3" s="3">
         <v>136</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3381,34 +3557,34 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C4" s="3">
         <v>51</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3416,34 +3592,34 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="C5" s="3">
         <v>37</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3451,34 +3627,34 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="C6" s="3">
         <v>40</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3486,34 +3662,34 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="C7" s="3">
         <v>150</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3521,34 +3697,34 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="C8" s="3">
         <v>51</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3556,34 +3732,34 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="C9" s="3">
         <v>56</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3591,34 +3767,34 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="C10" s="3">
         <v>4</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3626,34 +3802,34 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C11" s="3">
         <v>127</v>
       </c>
       <c r="D11" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="K11" s="3" t="s">
         <v>235</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3661,34 +3837,34 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="C12" s="3">
         <v>52</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3696,34 +3872,34 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="C13" s="3">
         <v>61</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3731,34 +3907,34 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="C14" s="3">
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3766,34 +3942,34 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="C15" s="3">
         <v>144</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3801,34 +3977,34 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="C16" s="3">
         <v>35</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3836,34 +4012,34 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="C17" s="3">
         <v>24</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
     </row>
     <row r="18" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3871,34 +4047,34 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="C18" s="3">
         <v>36</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
     </row>
     <row r="19" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3906,34 +4082,34 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="C19" s="3">
         <v>40</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
     </row>
     <row r="20" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3941,34 +4117,34 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="C20" s="3">
         <v>108</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
     </row>
     <row r="21" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3976,34 +4152,34 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="C21" s="3">
         <v>10</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
     </row>
     <row r="22" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4011,34 +4187,34 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="C22" s="3">
         <v>16</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
     </row>
     <row r="23" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4046,34 +4222,34 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="C23" s="3">
         <v>87</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
     </row>
     <row r="24" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4081,34 +4257,34 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="C24" s="3">
         <v>61</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4116,34 +4292,34 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="C25" s="3">
         <v>114</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
     </row>
     <row r="26" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4151,34 +4327,34 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C26" s="3">
         <v>15</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
     </row>
     <row r="27" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4186,34 +4362,34 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="C27" s="3">
         <v>52</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
     </row>
     <row r="28" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4221,34 +4397,34 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="C28" s="3">
         <v>14</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
     </row>
     <row r="29" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4256,34 +4432,34 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="C29" s="3">
         <v>73</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
     </row>
     <row r="30" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4291,34 +4467,34 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C30" s="3">
         <v>80</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
     </row>
     <row r="31" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4326,34 +4502,34 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="C31" s="3">
         <v>200</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
     </row>
     <row r="32" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4361,34 +4537,34 @@
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="C32" s="3">
         <v>57</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
     </row>
     <row r="33" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4396,34 +4572,34 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="C33" s="3">
         <v>39</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
     </row>
     <row r="34" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4431,34 +4607,34 @@
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="C34" s="3">
         <v>4</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
     </row>
     <row r="35" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4466,34 +4642,34 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C35" s="3">
         <v>26</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
     </row>
     <row r="36" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4501,34 +4677,34 @@
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="C36" s="3">
         <v>180</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
     </row>
     <row r="37" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4536,34 +4712,34 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="C37" s="3">
         <v>128</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>

--- a/docs/dominio-metrico/migracion/cuestionarios/la-gran-semiramis.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/la-gran-semiramis.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="239">
   <si>
     <t>Migración métrica · La gran Semíramis</t>
   </si>
@@ -27,7 +27,7 @@
     <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, donde estás ahora. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
   </si>
   <si>
-    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta. Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato. Las preguntas que se refieren a cada estrofa aparecen de dos maneras: si son pocas estrofas, hay una fila por estrofa; si son muchas, hay una sola fila cuya respuesta vale para todas, y las estrofas que se aparten de ella se anotan en «Excepciones / detalle» indicando los versos y la respuesta, por ejemplo «191–194: Cruzada · abab; 203–206: Cruzada · abab».</t>
+    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta, también cuando la pregunta es de cada estrofa: se contesta una vez y la respuesta vale para todas, y las estrofas que se aparten se anotan en «Excepciones / detalle» como «versos: esquema», por ejemplo «191-194: abab; 203-206: abab». Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato.</t>
   </si>
   <si>
     <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiré a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
@@ -54,7 +54,7 @@
     <t>Esquema de rima: una letra por verso, en mayúscula si el verso es de arte mayor y un guion si queda suelto. Por ejemplo, «aBab-B».</t>
   </si>
   <si>
-    <t>Excepciones: los versos de la estrofa y la respuesta que le corresponde, separando cada estrofa con punto y coma. Por ejemplo, «191–194: Cruzada · abab; 203–206: Cruzada · abab».</t>
+    <t>Excepciones: los versos de la estrofa y su esquema, separados por dos puntos, y cada estrofa de la siguiente con punto y coma. Por ejemplo, «191-194: abab; 203-206: abab». El esquema se escribe como arriba: una letra por verso, en mayúscula si el verso es de arte mayor.</t>
   </si>
   <si>
     <t>lista</t>
@@ -189,7 +189,7 @@
     <t>Esquema de rima · todas las estrofas</t>
   </si>
   <si>
-    <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones» (versos: respuesta). Cuántas estrofas son depende de lo que decidas arriba, así que contéstalo para todas</t>
+    <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones», como «191-194: abab». Cuántas estrofas son depende de lo que decidas arriba, así que contéstalo para todas</t>
   </si>
   <si>
     <t>R|e8af1e55-7dc2-4b1b-92d2-99a9f83bc0df|08db5aaa-4193-4fca-9e97-02134010c9c6</t>
@@ -198,7 +198,7 @@
     <t>Medida de cada verso · todas las estrofas</t>
   </si>
   <si>
-    <t>Escribe el número de sílabas de cada verso, en orden y separados por espacios («7 11 7 7 11»). La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones» (versos: respuesta). Cuántas estrofas son depende de lo que decidas arriba, así que contéstalo para todas</t>
+    <t>Escribe el número de sílabas de cada verso, en orden y separados por espacios («7 11 7 7 11»). La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones», como «568-575: 7 11 7 7 11». Cuántas estrofas son depende de lo que decidas arriba, así que contéstalo para todas</t>
   </si>
   <si>
     <t>R|e8af1e55-7dc2-4b1b-92d2-99a9f83bc0df|940d5240-1878-4da4-bc33-c068238be4ef</t>
@@ -210,103 +210,13 @@
     <t>Quintilla · Octosílaba consonante</t>
   </si>
   <si>
-    <t>Esquema de rima · estrofa 1 (vv. 1642–1646)</t>
-  </si>
-  <si>
-    <t>Elige en el desplegable</t>
-  </si>
-  <si>
-    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1642</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 2 (vv. 1647–1651)</t>
-  </si>
-  <si>
-    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1647</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 3 (vv. 1652–1656)</t>
-  </si>
-  <si>
-    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1652</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 4 (vv. 1657–1661)</t>
-  </si>
-  <si>
-    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1657</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 5 (vv. 1662–1666)</t>
-  </si>
-  <si>
-    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1662</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 6 (vv. 1667–1671)</t>
-  </si>
-  <si>
-    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1667</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 7 (vv. 1672–1676)</t>
-  </si>
-  <si>
-    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1672</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 8 (vv. 1677–1681)</t>
-  </si>
-  <si>
-    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1677</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 9 (vv. 1682–1686)</t>
-  </si>
-  <si>
-    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1682</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 10 (vv. 1687–1691)</t>
-  </si>
-  <si>
-    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1687</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 11 (vv. 1692–1696)</t>
-  </si>
-  <si>
-    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1692</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 12 (vv. 1697–1701)</t>
-  </si>
-  <si>
-    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1697</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 13 (vv. 1702–1706)</t>
-  </si>
-  <si>
-    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1702</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 14 (vv. 1707–1711)</t>
-  </si>
-  <si>
-    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1707</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 15 (vv. 1712–1716)</t>
-  </si>
-  <si>
-    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1712</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 16 (vv. 1717–1721)</t>
-  </si>
-  <si>
-    <t>U|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066|1717</t>
+    <t>Esquema de rima · 16 estrofas</t>
+  </si>
+  <si>
+    <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones», como «191-194: abab»</t>
+  </si>
+  <si>
+    <t>R|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066</t>
   </si>
   <si>
     <t>1979–2017</t>
@@ -1446,7 +1356,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="11" customWidth="1"/>
@@ -1689,19 +1599,19 @@
         <v>55</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>44</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>44</v>
@@ -1713,7 +1623,7 @@
         <v>44</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1721,19 +1631,19 @@
         <v>55</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>44</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>44</v>
@@ -1745,7 +1655,7 @@
         <v>44</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1753,19 +1663,19 @@
         <v>55</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>44</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>44</v>
@@ -1777,7 +1687,7 @@
         <v>44</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1785,19 +1695,19 @@
         <v>55</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>44</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>44</v>
@@ -1809,502 +1719,19 @@
         <v>44</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D13" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J22" s="7" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J24" s="7" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J26" s="7" t="s">
-        <v>107</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G10:G22">
-      <formula1>Listas!$C$2:$C$9</formula1>
-    </dataValidation>
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G2:G4">
       <formula1>Listas!$A$2:$A$5</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G5">
       <formula1>Listas!$B$2:$B$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G7:G22">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G7">
       <formula1>Listas!$C$2:$C$9</formula1>
     </dataValidation>
   </dataValidations>
@@ -2337,19 +1764,19 @@
         <v>32</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>36</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>38</v>
@@ -2360,19 +1787,19 @@
     </row>
     <row r="2" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>44</v>
@@ -2384,24 +1811,24 @@
         <v>44</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>118</v>
+        <v>88</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>44</v>
@@ -2413,24 +1840,24 @@
         <v>44</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>123</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>124</v>
+        <v>94</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>44</v>
@@ -2442,24 +1869,24 @@
         <v>44</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>126</v>
+        <v>96</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>44</v>
@@ -2471,24 +1898,24 @@
         <v>44</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>132</v>
+        <v>102</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>44</v>
@@ -2500,24 +1927,24 @@
         <v>44</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>133</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>134</v>
+        <v>104</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>44</v>
@@ -2529,24 +1956,24 @@
         <v>44</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>135</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>44</v>
@@ -2558,24 +1985,24 @@
         <v>44</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>138</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>139</v>
+        <v>109</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>44</v>
@@ -2587,24 +2014,24 @@
         <v>44</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>140</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>141</v>
+        <v>111</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>44</v>
@@ -2616,24 +2043,24 @@
         <v>44</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>142</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>44</v>
@@ -2645,24 +2072,24 @@
         <v>44</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>145</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>44</v>
@@ -2674,53 +2101,53 @@
         <v>44</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>147</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>148</v>
+        <v>118</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="E13" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I13" s="7" t="s">
         <v>120</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>44</v>
@@ -2732,24 +2159,24 @@
         <v>44</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>152</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>154</v>
+        <v>124</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>44</v>
@@ -2761,24 +2188,24 @@
         <v>44</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>155</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>156</v>
+        <v>126</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>44</v>
@@ -2790,24 +2217,24 @@
         <v>44</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>157</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>158</v>
+        <v>128</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>159</v>
+        <v>129</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>44</v>
@@ -2819,24 +2246,24 @@
         <v>44</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>160</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>162</v>
+        <v>132</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>163</v>
+        <v>133</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>164</v>
+        <v>134</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>44</v>
@@ -2848,24 +2275,24 @@
         <v>44</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>165</v>
+        <v>135</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>44</v>
@@ -2877,24 +2304,24 @@
         <v>44</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
     </row>
     <row r="20" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>44</v>
@@ -2906,24 +2333,24 @@
         <v>44</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>170</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>171</v>
+        <v>141</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>44</v>
@@ -2935,53 +2362,53 @@
         <v>44</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>172</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>173</v>
+        <v>143</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="D22" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I22" s="7" t="s">
         <v>144</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="23" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>175</v>
+        <v>145</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>176</v>
+        <v>146</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>177</v>
+        <v>147</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>178</v>
+        <v>148</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>44</v>
@@ -2993,7 +2420,7 @@
         <v>44</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
     </row>
     <row r="24" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3004,13 +2431,13 @@
         <v>48</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>181</v>
+        <v>151</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>182</v>
+        <v>152</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>44</v>
@@ -3022,24 +2449,24 @@
         <v>44</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>183</v>
+        <v>153</v>
       </c>
     </row>
     <row r="25" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>184</v>
+        <v>154</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>185</v>
+        <v>155</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>44</v>
@@ -3051,24 +2478,24 @@
         <v>44</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>186</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>187</v>
+        <v>157</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>181</v>
+        <v>151</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>182</v>
+        <v>152</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>44</v>
@@ -3080,24 +2507,24 @@
         <v>44</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>188</v>
+        <v>158</v>
       </c>
     </row>
     <row r="27" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>189</v>
+        <v>159</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>44</v>
@@ -3109,24 +2536,24 @@
         <v>44</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>191</v>
+        <v>161</v>
       </c>
     </row>
     <row r="28" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>192</v>
+        <v>162</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>193</v>
+        <v>163</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>44</v>
@@ -3138,24 +2565,24 @@
         <v>44</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>194</v>
+        <v>164</v>
       </c>
     </row>
     <row r="29" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>195</v>
+        <v>165</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="F29" s="6" t="s">
         <v>44</v>
@@ -3167,24 +2594,24 @@
         <v>44</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>196</v>
+        <v>166</v>
       </c>
     </row>
     <row r="30" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>197</v>
+        <v>167</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>44</v>
@@ -3196,24 +2623,24 @@
         <v>44</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>198</v>
+        <v>168</v>
       </c>
     </row>
     <row r="31" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>199</v>
+        <v>169</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="F31" s="6" t="s">
         <v>44</v>
@@ -3225,24 +2652,24 @@
         <v>44</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>200</v>
+        <v>170</v>
       </c>
     </row>
     <row r="32" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>201</v>
+        <v>171</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>202</v>
+        <v>172</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>44</v>
@@ -3254,7 +2681,7 @@
         <v>44</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -3297,22 +2724,22 @@
         <v>31</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>204</v>
+        <v>174</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>205</v>
+        <v>175</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>206</v>
+        <v>176</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>207</v>
+        <v>177</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>208</v>
+        <v>178</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="I1" s="5" t="s">
         <v>38</v>
@@ -3323,22 +2750,22 @@
     </row>
     <row r="2" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>209</v>
+        <v>179</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>171</v>
+        <v>141</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>211</v>
+        <v>181</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>212</v>
+        <v>182</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>213</v>
+        <v>183</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>44</v>
@@ -3350,27 +2777,27 @@
         <v>44</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>214</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>209</v>
+        <v>179</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>215</v>
+        <v>185</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>211</v>
+        <v>181</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>216</v>
+        <v>186</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>213</v>
+        <v>183</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>44</v>
@@ -3382,27 +2809,27 @@
         <v>44</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>217</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>209</v>
+        <v>179</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>218</v>
+        <v>188</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>211</v>
+        <v>181</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>219</v>
+        <v>189</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>213</v>
+        <v>183</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>44</v>
@@ -3414,7 +2841,7 @@
         <v>44</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>220</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -3449,37 +2876,37 @@
   <sheetData>
     <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>221</v>
+        <v>191</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>222</v>
+        <v>192</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>32</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>223</v>
+        <v>193</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>224</v>
+        <v>194</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>225</v>
+        <v>195</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>226</v>
+        <v>196</v>
       </c>
       <c r="J1" s="5" t="s">
         <v>34</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>227</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3487,34 +2914,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="C2" s="3">
         <v>38</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>229</v>
+        <v>199</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>231</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3522,34 +2949,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>118</v>
+        <v>88</v>
       </c>
       <c r="C3" s="3">
         <v>136</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>232</v>
+        <v>202</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>233</v>
+        <v>203</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>234</v>
+        <v>204</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>235</v>
+        <v>205</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3557,34 +2984,34 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>124</v>
+        <v>94</v>
       </c>
       <c r="C4" s="3">
         <v>51</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>229</v>
+        <v>199</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>231</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3592,34 +3019,34 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>126</v>
+        <v>96</v>
       </c>
       <c r="C5" s="3">
         <v>37</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>236</v>
+        <v>206</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>237</v>
+        <v>207</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>238</v>
+        <v>208</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>235</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3627,34 +3054,34 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>132</v>
+        <v>102</v>
       </c>
       <c r="C6" s="3">
         <v>40</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>229</v>
+        <v>199</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>231</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3662,34 +3089,34 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>239</v>
+        <v>209</v>
       </c>
       <c r="C7" s="3">
         <v>150</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>241</v>
+        <v>211</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>242</v>
+        <v>212</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>243</v>
+        <v>213</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>244</v>
+        <v>214</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>245</v>
+        <v>215</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>235</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3697,34 +3124,34 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>134</v>
+        <v>104</v>
       </c>
       <c r="C8" s="3">
         <v>51</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>229</v>
+        <v>199</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>231</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3732,34 +3159,34 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="C9" s="3">
         <v>56</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>232</v>
+        <v>202</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>233</v>
+        <v>203</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>246</v>
+        <v>216</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>235</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3767,34 +3194,34 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>139</v>
+        <v>109</v>
       </c>
       <c r="C10" s="3">
         <v>4</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>229</v>
+        <v>199</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>231</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3808,28 +3235,28 @@
         <v>127</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>247</v>
+        <v>217</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>248</v>
+        <v>218</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>249</v>
+        <v>219</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>235</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3837,34 +3264,34 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>141</v>
+        <v>111</v>
       </c>
       <c r="C12" s="3">
         <v>52</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>229</v>
+        <v>199</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>231</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3872,34 +3299,34 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="C13" s="3">
         <v>61</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>236</v>
+        <v>206</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>237</v>
+        <v>207</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>238</v>
+        <v>208</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>235</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3907,34 +3334,34 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="C14" s="3">
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>229</v>
+        <v>199</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>231</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3942,34 +3369,34 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>148</v>
+        <v>118</v>
       </c>
       <c r="C15" s="3">
         <v>144</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>232</v>
+        <v>202</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>233</v>
+        <v>203</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>251</v>
+        <v>221</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>235</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3977,34 +3404,34 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="C16" s="3">
         <v>35</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>229</v>
+        <v>199</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>231</v>
+        <v>201</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4012,34 +3439,34 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="C17" s="3">
         <v>24</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>232</v>
+        <v>202</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>233</v>
+        <v>203</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>235</v>
+        <v>205</v>
       </c>
     </row>
     <row r="18" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4047,34 +3474,34 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>156</v>
+        <v>126</v>
       </c>
       <c r="C18" s="3">
         <v>36</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>229</v>
+        <v>199</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>231</v>
+        <v>201</v>
       </c>
     </row>
     <row r="19" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4082,34 +3509,34 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>158</v>
+        <v>128</v>
       </c>
       <c r="C19" s="3">
         <v>40</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>232</v>
+        <v>202</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>233</v>
+        <v>203</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>252</v>
+        <v>222</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>235</v>
+        <v>205</v>
       </c>
     </row>
     <row r="20" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4117,34 +3544,34 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="C20" s="3">
         <v>108</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>164</v>
+        <v>134</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>253</v>
+        <v>223</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>254</v>
+        <v>224</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>255</v>
+        <v>225</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>235</v>
+        <v>205</v>
       </c>
     </row>
     <row r="21" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4152,34 +3579,34 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="C21" s="3">
         <v>10</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>229</v>
+        <v>199</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>231</v>
+        <v>201</v>
       </c>
     </row>
     <row r="22" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4187,34 +3614,34 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="C22" s="3">
         <v>16</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>232</v>
+        <v>202</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>233</v>
+        <v>203</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>235</v>
+        <v>205</v>
       </c>
     </row>
     <row r="23" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4222,34 +3649,34 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>171</v>
+        <v>141</v>
       </c>
       <c r="C23" s="3">
         <v>87</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>229</v>
+        <v>199</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>211</v>
+        <v>181</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>231</v>
+        <v>201</v>
       </c>
     </row>
     <row r="24" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4257,34 +3684,34 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>173</v>
+        <v>143</v>
       </c>
       <c r="C24" s="3">
         <v>61</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>236</v>
+        <v>206</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>237</v>
+        <v>207</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>238</v>
+        <v>208</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>235</v>
+        <v>205</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4292,34 +3719,34 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>175</v>
+        <v>145</v>
       </c>
       <c r="C25" s="3">
         <v>114</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>258</v>
+        <v>228</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>259</v>
+        <v>229</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>235</v>
+        <v>205</v>
       </c>
     </row>
     <row r="26" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4333,28 +3760,28 @@
         <v>15</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>182</v>
+        <v>152</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>238</v>
+        <v>208</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>261</v>
+        <v>231</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>235</v>
+        <v>205</v>
       </c>
     </row>
     <row r="27" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4362,34 +3789,34 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>184</v>
+        <v>154</v>
       </c>
       <c r="C27" s="3">
         <v>52</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>236</v>
+        <v>206</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>237</v>
+        <v>207</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>238</v>
+        <v>208</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>235</v>
+        <v>205</v>
       </c>
     </row>
     <row r="28" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4397,34 +3824,34 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>187</v>
+        <v>157</v>
       </c>
       <c r="C28" s="3">
         <v>14</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>182</v>
+        <v>152</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>238</v>
+        <v>208</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>235</v>
+        <v>205</v>
       </c>
     </row>
     <row r="29" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4432,34 +3859,34 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>189</v>
+        <v>159</v>
       </c>
       <c r="C29" s="3">
         <v>73</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>236</v>
+        <v>206</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>237</v>
+        <v>207</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>238</v>
+        <v>208</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>235</v>
+        <v>205</v>
       </c>
     </row>
     <row r="30" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4473,28 +3900,28 @@
         <v>80</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>241</v>
+        <v>211</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>242</v>
+        <v>212</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>235</v>
+        <v>205</v>
       </c>
     </row>
     <row r="31" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4502,34 +3929,34 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>192</v>
+        <v>162</v>
       </c>
       <c r="C31" s="3">
         <v>200</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>232</v>
+        <v>202</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>233</v>
+        <v>203</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>263</v>
+        <v>233</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>235</v>
+        <v>205</v>
       </c>
     </row>
     <row r="32" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4537,34 +3964,34 @@
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>195</v>
+        <v>165</v>
       </c>
       <c r="C32" s="3">
         <v>57</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>229</v>
+        <v>199</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>231</v>
+        <v>201</v>
       </c>
     </row>
     <row r="33" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4572,34 +3999,34 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="C33" s="3">
         <v>39</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>264</v>
+        <v>234</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>265</v>
+        <v>235</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>266</v>
+        <v>236</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>211</v>
+        <v>181</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>235</v>
+        <v>205</v>
       </c>
     </row>
     <row r="34" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4607,34 +4034,34 @@
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>197</v>
+        <v>167</v>
       </c>
       <c r="C34" s="3">
         <v>4</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>229</v>
+        <v>199</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>231</v>
+        <v>201</v>
       </c>
     </row>
     <row r="35" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4648,28 +4075,28 @@
         <v>26</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>264</v>
+        <v>234</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>265</v>
+        <v>235</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>266</v>
+        <v>236</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>211</v>
+        <v>181</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>267</v>
+        <v>237</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>235</v>
+        <v>205</v>
       </c>
     </row>
     <row r="36" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4677,34 +4104,34 @@
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>199</v>
+        <v>169</v>
       </c>
       <c r="C36" s="3">
         <v>180</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>229</v>
+        <v>199</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>231</v>
+        <v>201</v>
       </c>
     </row>
     <row r="37" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4712,34 +4139,34 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>201</v>
+        <v>171</v>
       </c>
       <c r="C37" s="3">
         <v>128</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>232</v>
+        <v>202</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>233</v>
+        <v>203</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>268</v>
+        <v>238</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>235</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>

--- a/docs/dominio-metrico/migracion/cuestionarios/la-gran-semiramis.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/la-gran-semiramis.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="234">
   <si>
     <t>Migración métrica · La gran Semíramis</t>
   </si>
@@ -27,7 +27,7 @@
     <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, donde estás ahora. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
   </si>
   <si>
-    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta, también cuando la pregunta es de cada estrofa: se contesta una vez y la respuesta vale para todas, y las estrofas que se aparten se anotan en «Excepciones / detalle» como «versos: esquema», por ejemplo «191-194: abab; 203-206: abab». Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato.</t>
+    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta, también cuando la pregunta es de cada estrofa: se contesta una vez y la respuesta vale para todas, y las estrofas que se aparten se anotan en «Excepciones / detalle». Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» dice el formato y da un ejemplo.</t>
   </si>
   <si>
     <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiré a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
@@ -42,21 +42,6 @@
     <t>Si algo no está claro o no sabes cómo contestarlo, pregúntamelo antes de dejarlo a medias. Una vez hecha la migración podrás ver cada secuencia de tu obra con el editor nuevo en el dashboard y comprobar allí que la migración no dejó ningún hueco.</t>
   </si>
   <si>
-    <t>Cuando no hay desplegable, los formatos son estos:</t>
-  </si>
-  <si>
-    <t>Medidas: el número de sílabas de cada verso, en orden y separados por espacios. Por ejemplo, «7 11 7 7 11 7 11 11».</t>
-  </si>
-  <si>
-    <t>Posiciones: en qué versos de la estrofa cae el quebrado y cuántas sílabas tiene cada uno, separados por comas. Por ejemplo, «3: 4, 8: 5» quiere decir que el verso 3 tiene cuatro sílabas y el 8 tiene cinco.</t>
-  </si>
-  <si>
-    <t>Esquema de rima: una letra por verso, en mayúscula si el verso es de arte mayor y un guion si queda suelto. Por ejemplo, «aBab-B».</t>
-  </si>
-  <si>
-    <t>Excepciones: los versos de la estrofa y su esquema, separados por dos puntos, y cada estrofa de la siguiente con punto y coma. Por ejemplo, «191-194: abab; 203-206: abab». El esquema se escribe como arriba: una letra por verso, en mayúscula si el verso es de arte mayor.</t>
-  </si>
-  <si>
     <t>lista</t>
   </si>
   <si>
@@ -189,7 +174,7 @@
     <t>Esquema de rima · todas las estrofas</t>
   </si>
   <si>
-    <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones», como «191-194: abab». Cuántas estrofas son depende de lo que decidas arriba, así que contéstalo para todas</t>
+    <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones», una detrás de otra y separadas por punto y coma, como «191-194: abab; 203-206: abab». Cuántas estrofas son depende de lo que decidas arriba, así que contéstalo para todas</t>
   </si>
   <si>
     <t>R|e8af1e55-7dc2-4b1b-92d2-99a9f83bc0df|08db5aaa-4193-4fca-9e97-02134010c9c6</t>
@@ -198,7 +183,7 @@
     <t>Medida de cada verso · todas las estrofas</t>
   </si>
   <si>
-    <t>Escribe el número de sílabas de cada verso, en orden y separados por espacios («7 11 7 7 11»). La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones», como «568-575: 7 11 7 7 11». Cuántas estrofas son depende de lo que decidas arriba, así que contéstalo para todas</t>
+    <t>Escribe el número de sílabas de cada verso, en orden y separados por espacios («7 11 7 7 11»). La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones», una detrás de otra y separadas por punto y coma, como «568-575: 7 11 7 7 11; 592-599: 7 7 11 11 7». Cuántas estrofas son depende de lo que decidas arriba, así que contéstalo para todas</t>
   </si>
   <si>
     <t>R|e8af1e55-7dc2-4b1b-92d2-99a9f83bc0df|940d5240-1878-4da4-bc33-c068238be4ef</t>
@@ -213,7 +198,7 @@
     <t>Esquema de rima · 16 estrofas</t>
   </si>
   <si>
-    <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones», como «191-194: abab»</t>
+    <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones», una detrás de otra y separadas por punto y coma, como «191-194: abab; 203-206: abab»</t>
   </si>
   <si>
     <t>R|cc8b1b2c-97a5-4d28-87e1-0f2dd3397985|a43860ff-566c-4a0b-b210-4572b8d7b066</t>
@@ -826,14 +811,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1185,7 +1169,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
@@ -1229,31 +1213,6 @@
     <row r="9" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1272,80 +1231,80 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1370,356 +1329,356 @@
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="J1" s="4" t="s">
         <v>34</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="G2" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J2" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" s="6" t="s">
         <v>45</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>54</v>
+      <c r="G4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>58</v>
+        <v>52</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>61</v>
+      <c r="G6" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>66</v>
+        <v>60</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>70</v>
+        <v>64</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>73</v>
+      <c r="G9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>75</v>
+        <v>69</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D11" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>77</v>
+      <c r="G11" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1756,932 +1715,932 @@
     <col min="9" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>39</v>
+      <c r="E1" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I2" s="6" t="s">
         <v>82</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>95</v>
+        <v>81</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" s="6" t="s">
         <v>96</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>103</v>
+        <v>81</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>105</v>
+        <v>81</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>108</v>
+        <v>87</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>110</v>
+        <v>81</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>112</v>
+        <v>81</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>115</v>
+        <v>95</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>117</v>
+        <v>81</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>120</v>
+        <v>87</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>122</v>
+        <v>81</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>125</v>
+        <v>87</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>127</v>
+        <v>81</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>130</v>
+        <v>87</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>135</v>
+        <v>129</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>137</v>
+        <v>81</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="20" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>140</v>
+        <v>87</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>142</v>
+        <v>81</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="22" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>144</v>
+        <v>95</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="23" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I23" s="6" t="s">
         <v>145</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="24" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I24" s="7" t="s">
-        <v>153</v>
+        <v>147</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="25" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>156</v>
+        <v>95</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="26" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I26" s="7" t="s">
-        <v>158</v>
+        <v>147</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="27" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I27" s="7" t="s">
-        <v>161</v>
+        <v>95</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="28" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I28" s="7" t="s">
-        <v>164</v>
+        <v>87</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="29" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H29" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I29" s="7" t="s">
-        <v>166</v>
+        <v>81</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="30" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I30" s="7" t="s">
-        <v>168</v>
+        <v>81</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="31" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H31" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I31" s="7" t="s">
-        <v>170</v>
+        <v>81</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="32" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I32" s="7" t="s">
-        <v>173</v>
+        <v>87</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -2716,132 +2675,132 @@
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>39</v>
+    <row r="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J2" s="6" t="s">
         <v>179</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>186</v>
-      </c>
       <c r="F3" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>187</v>
+        <v>178</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>190</v>
+        <v>178</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -2874,39 +2833,39 @@
     <col min="11" max="11" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" s="5" t="s">
+      <c r="J1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>192</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2914,34 +2873,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C2" s="3">
         <v>38</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2949,34 +2908,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C3" s="3">
         <v>136</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2984,34 +2943,34 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C4" s="3">
         <v>51</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3019,34 +2978,34 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C5" s="3">
         <v>37</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3054,34 +3013,34 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C6" s="3">
         <v>40</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3089,34 +3048,34 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C7" s="3">
         <v>150</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="K7" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3124,34 +3083,34 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C8" s="3">
         <v>51</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3159,34 +3118,34 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C9" s="3">
         <v>56</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3194,34 +3153,34 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C10" s="3">
         <v>4</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3229,34 +3188,34 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C11" s="3">
         <v>127</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3264,34 +3223,34 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C12" s="3">
         <v>52</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3299,34 +3258,34 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C13" s="3">
         <v>61</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3334,34 +3293,34 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C14" s="3">
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3369,34 +3328,34 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C15" s="3">
         <v>144</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3404,34 +3363,34 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C16" s="3">
         <v>35</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3439,34 +3398,34 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C17" s="3">
         <v>24</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J17" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="K17" s="3" t="s">
         <v>200</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="18" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3474,34 +3433,34 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C18" s="3">
         <v>36</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="19" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3509,34 +3468,34 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C19" s="3">
         <v>40</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="20" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3544,34 +3503,34 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C20" s="3">
         <v>108</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="21" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3579,34 +3538,34 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C21" s="3">
         <v>10</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="22" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3614,34 +3573,34 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C22" s="3">
         <v>16</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="23" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3649,34 +3608,34 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C23" s="3">
         <v>87</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="24" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3684,34 +3643,34 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C24" s="3">
         <v>61</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3719,34 +3678,34 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C25" s="3">
         <v>114</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="26" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3754,34 +3713,34 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C26" s="3">
         <v>15</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="27" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3789,34 +3748,34 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C27" s="3">
         <v>52</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="28" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3824,34 +3783,34 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C28" s="3">
         <v>14</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="29" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3859,34 +3818,34 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C29" s="3">
         <v>73</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="30" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3894,34 +3853,34 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C30" s="3">
         <v>80</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="31" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3929,34 +3888,34 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C31" s="3">
         <v>200</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="32" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3964,34 +3923,34 @@
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C32" s="3">
         <v>57</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="33" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3999,34 +3958,34 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C33" s="3">
         <v>39</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="34" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4034,34 +3993,34 @@
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C34" s="3">
         <v>4</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="35" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4069,34 +4028,34 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C35" s="3">
         <v>26</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="36" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4104,34 +4063,34 @@
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C36" s="3">
         <v>180</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="37" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4139,34 +4098,34 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C37" s="3">
         <v>128</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
